--- a/public/cent_health_parameters.xlsx
+++ b/public/cent_health_parameters.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Reproductive Health</t>
+          <t>Bone, Muscle &amp; Joint Health</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Bone, Muscle &amp; Joint Health</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>Lung &amp; Respiratory Health</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Vascular Health</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -678,11 +678,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>CT Calcium Score</t>
@@ -753,11 +748,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>DEXA Scan</t>
@@ -828,11 +818,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>DEXA Scan</t>
@@ -903,11 +888,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -978,11 +958,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1053,11 +1028,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1128,11 +1098,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1203,11 +1168,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1278,11 +1238,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1353,11 +1308,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1428,11 +1378,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1503,11 +1448,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1578,11 +1518,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1653,11 +1588,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1728,11 +1658,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1803,11 +1728,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1878,11 +1798,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -1953,11 +1868,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2028,11 +1938,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2103,11 +2008,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2178,11 +2078,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2253,11 +2148,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2318,17 +2208,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2403,11 +2288,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2468,17 +2348,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2553,11 +2428,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2628,11 +2498,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2703,11 +2568,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2778,11 +2638,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2853,11 +2708,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -2928,11 +2778,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>DEXA Scan</t>
@@ -3003,11 +2848,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>DEXA Scan</t>
@@ -3078,11 +2918,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>DEXA Scan</t>
@@ -3153,11 +2988,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>DEXA Scan</t>
@@ -3228,11 +3058,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -3303,11 +3128,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -3373,12 +3193,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3453,11 +3268,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -3528,11 +3338,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -3593,17 +3398,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3668,17 +3468,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K42" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3753,11 +3548,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -3828,11 +3618,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -3903,11 +3688,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -3978,11 +3758,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4053,11 +3828,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4128,11 +3898,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4203,11 +3968,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M49" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4278,11 +4038,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M50" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4353,11 +4108,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M51" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4428,11 +4178,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M52" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4503,11 +4248,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M53" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4578,11 +4318,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M54" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4653,11 +4388,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M55" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4728,11 +4458,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M56" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4803,11 +4528,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M57" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4878,11 +4598,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M58" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -4953,11 +4668,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M59" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5028,11 +4738,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M60" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5103,11 +4808,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M61" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5178,11 +4878,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M62" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5253,11 +4948,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M63" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5328,11 +5018,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M64" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5403,11 +5088,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M65" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5478,11 +5158,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M66" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5553,11 +5228,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5628,11 +5298,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M68" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5703,11 +5368,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M69" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5768,17 +5428,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M70" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5853,11 +5508,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M71" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -5928,11 +5578,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M72" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -6003,11 +5648,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M73" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -6078,11 +5718,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M74" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -6153,11 +5788,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M75" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -6228,11 +5858,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M76" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -6303,11 +5928,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M77" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -6378,11 +5998,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M78" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -6453,11 +6068,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M79" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -6528,11 +6138,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M80" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -6603,11 +6208,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M81" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -6678,11 +6278,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M82" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -6753,11 +6348,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M83" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -6828,11 +6418,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M84" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -6903,11 +6488,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M85" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -6978,11 +6558,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M86" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -7053,11 +6628,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M87" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -7128,11 +6698,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M88" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -7203,11 +6768,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M89" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -7278,11 +6838,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M90" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -7353,11 +6908,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M91" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -7428,11 +6978,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M92" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -7503,11 +7048,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M93" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -7578,11 +7118,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M94" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -7653,11 +7188,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M95" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -7728,11 +7258,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M96" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -7803,11 +7328,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M97" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -7878,11 +7398,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M98" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -7953,11 +7468,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M99" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8028,11 +7538,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M100" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8103,11 +7608,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M101" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8178,11 +7678,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M102" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8253,11 +7748,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M103" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8328,11 +7818,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M104" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8403,11 +7888,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M105" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8478,11 +7958,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M106" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8553,11 +8028,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M107" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8628,11 +8098,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M108" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8703,11 +8168,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M109" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8778,11 +8238,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M110" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8853,11 +8308,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M111" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -8928,11 +8378,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M112" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9003,11 +8448,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M113" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9078,11 +8518,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M114" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9153,11 +8588,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M115" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9228,11 +8658,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M116" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9303,11 +8728,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9378,11 +8798,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M118" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9453,11 +8868,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M119" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9518,17 +8928,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K120" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M120" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -9603,11 +9008,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M121" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9678,11 +9078,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M122" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9753,11 +9148,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M123" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9828,11 +9218,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M124" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9903,11 +9288,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M125" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -9978,11 +9358,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M126" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -10053,11 +9428,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M127" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -10128,11 +9498,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M128" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -10203,11 +9568,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M129" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -10278,11 +9638,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M130" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -10353,11 +9708,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M131" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -10428,11 +9778,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M132" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -10503,11 +9848,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M133" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -10578,11 +9918,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M134" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
           <t>Urine Analysis</t>
@@ -10653,11 +9988,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M135" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -10728,11 +10058,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M136" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
           <t>Blood Test</t>
@@ -10803,11 +10128,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M137" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
           <t>ECG</t>
@@ -10868,17 +10188,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K138" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L138" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M138" s="6" t="inlineStr">
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L138" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -10943,17 +10258,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K139" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L139" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M139" s="6" t="inlineStr">
+      <c r="K139" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L139" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11018,17 +10328,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K140" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L140" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M140" s="6" t="inlineStr">
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L140" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11093,17 +10398,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K141" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L141" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M141" s="6" t="inlineStr">
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L141" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11168,17 +10468,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K142" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L142" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M142" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11243,17 +10538,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K143" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M143" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11318,17 +10608,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K144" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L144" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M144" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11393,17 +10678,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K145" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M145" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11468,17 +10748,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K146" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L146" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M146" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11543,17 +10818,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K147" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M147" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11618,17 +10888,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K148" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L148" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M148" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11693,17 +10958,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K149" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M149" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11768,17 +11028,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K150" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L150" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M150" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11843,17 +11098,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K151" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M151" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11918,17 +11168,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K152" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L152" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M152" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11993,17 +11238,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K153" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M153" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -12033,11 +11273,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="D154" s="6" t="n"/>
       <c r="E154" s="6" t="inlineStr">
         <is>
           <t>No</t>
@@ -12078,9 +11314,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M154" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12143,17 +11379,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K155" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L155" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M155" s="6" t="inlineStr">
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L155" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -12228,11 +11459,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M156" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -12303,11 +11529,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M157" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -12378,11 +11599,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M158" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -12453,11 +11669,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M159" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -12528,11 +11739,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M160" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -12603,11 +11809,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M161" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -12678,11 +11879,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M162" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -12753,11 +11949,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M163" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -12828,11 +12019,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M164" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -12903,11 +12089,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M165" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -12978,11 +12159,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M166" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -13053,11 +12229,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M167" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -13128,11 +12299,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M168" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -13158,11 +12324,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="D169" s="6" t="n"/>
       <c r="E169" s="6" t="inlineStr">
         <is>
           <t>No</t>
@@ -13203,9 +12365,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M169" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -13278,11 +12440,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M170" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -13353,11 +12510,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M171" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -13428,11 +12580,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M172" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -13503,11 +12650,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M173" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -13578,11 +12720,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M174" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -13653,11 +12790,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M175" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -13683,11 +12815,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="D176" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D176" s="5" t="n"/>
       <c r="E176" s="6" t="inlineStr">
         <is>
           <t>No</t>
@@ -13728,9 +12856,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M176" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
@@ -13758,11 +12886,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="D177" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D177" s="5" t="n"/>
       <c r="E177" s="6" t="inlineStr">
         <is>
           <t>No</t>
@@ -13803,9 +12927,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M177" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
@@ -13833,11 +12957,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="D178" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D178" s="5" t="n"/>
       <c r="E178" s="6" t="inlineStr">
         <is>
           <t>No</t>
@@ -13878,9 +12998,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M178" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr">
@@ -13953,11 +13073,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M179" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N179" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -14028,11 +13143,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M180" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -14103,11 +13213,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M181" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N181" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -14178,11 +13283,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M182" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N182" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -14253,11 +13353,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M183" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N183" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -14283,11 +13378,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="D184" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D184" s="5" t="n"/>
       <c r="E184" s="6" t="inlineStr">
         <is>
           <t>No</t>
@@ -14328,9 +13419,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M184" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr">
@@ -14358,11 +13449,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="D185" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D185" s="5" t="n"/>
       <c r="E185" s="6" t="inlineStr">
         <is>
           <t>No</t>
@@ -14403,9 +13490,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M185" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N185" s="2" t="inlineStr">
@@ -14433,11 +13520,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="D186" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D186" s="5" t="n"/>
       <c r="E186" s="6" t="inlineStr">
         <is>
           <t>No</t>
@@ -14478,9 +13561,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M186" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
@@ -14553,11 +13636,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M187" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N187" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -14583,11 +13661,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="D188" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D188" s="5" t="n"/>
       <c r="E188" s="6" t="inlineStr">
         <is>
           <t>No</t>
@@ -14628,9 +13702,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M188" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N188" s="2" t="inlineStr">
@@ -14703,11 +13777,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M189" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N189" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -14778,11 +13847,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M190" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N190" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -14853,11 +13917,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M191" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N191" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -14928,11 +13987,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M192" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N192" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -14993,17 +14047,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K193" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L193" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M193" s="6" t="inlineStr">
+      <c r="K193" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L193" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -15068,17 +14117,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K194" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L194" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M194" s="6" t="inlineStr">
+      <c r="K194" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L194" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -15143,17 +14187,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K195" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L195" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M195" s="6" t="inlineStr">
+      <c r="K195" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L195" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -15218,17 +14257,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K196" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L196" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M196" s="6" t="inlineStr">
+      <c r="K196" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L196" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -15293,17 +14327,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K197" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L197" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M197" s="6" t="inlineStr">
+      <c r="K197" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L197" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -15368,17 +14397,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K198" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L198" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M198" s="6" t="inlineStr">
+      <c r="K198" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L198" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -15443,17 +14467,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K199" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L199" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M199" s="6" t="inlineStr">
+      <c r="K199" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L199" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -15518,17 +14537,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K200" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L200" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M200" s="6" t="inlineStr">
+      <c r="K200" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L200" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -15593,17 +14607,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K201" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L201" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M201" s="6" t="inlineStr">
+      <c r="K201" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L201" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -15668,17 +14677,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K202" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L202" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M202" s="6" t="inlineStr">
+      <c r="K202" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L202" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -15753,11 +14757,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M203" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -15828,11 +14827,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M204" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -15903,11 +14897,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M205" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -15978,11 +14967,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M206" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N206" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -16053,11 +15037,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M207" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N207" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -16128,11 +15107,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M208" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N208" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -16203,11 +15177,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M209" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -16278,11 +15247,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M210" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N210" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -16353,11 +15317,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M211" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N211" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -16428,11 +15387,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M212" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -16498,12 +15452,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L213" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M213" s="5" t="inlineStr">
+      <c r="L213" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -16573,12 +15522,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L214" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M214" s="5" t="inlineStr">
+      <c r="L214" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -16648,12 +15592,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L215" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M215" s="5" t="inlineStr">
+      <c r="L215" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -16723,12 +15662,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L216" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M216" s="5" t="inlineStr">
+      <c r="L216" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -16798,12 +15732,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L217" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M217" s="5" t="inlineStr">
+      <c r="L217" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -16873,12 +15802,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L218" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M218" s="5" t="inlineStr">
+      <c r="L218" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -16948,12 +15872,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L219" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M219" s="5" t="inlineStr">
+      <c r="L219" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17023,12 +15942,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L220" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M220" s="5" t="inlineStr">
+      <c r="L220" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17098,12 +16012,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L221" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M221" s="5" t="inlineStr">
+      <c r="L221" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17173,12 +16082,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L222" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M222" s="5" t="inlineStr">
+      <c r="L222" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17248,12 +16152,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L223" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M223" s="5" t="inlineStr">
+      <c r="L223" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17323,12 +16222,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L224" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M224" s="5" t="inlineStr">
+      <c r="L224" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17398,12 +16292,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L225" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M225" s="5" t="inlineStr">
+      <c r="L225" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17473,12 +16362,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L226" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M226" s="5" t="inlineStr">
+      <c r="L226" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17548,12 +16432,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L227" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M227" s="5" t="inlineStr">
+      <c r="L227" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17623,12 +16502,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L228" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M228" s="5" t="inlineStr">
+      <c r="L228" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17698,12 +16572,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L229" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M229" s="5" t="inlineStr">
+      <c r="L229" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17773,12 +16642,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L230" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M230" s="5" t="inlineStr">
+      <c r="L230" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17848,12 +16712,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L231" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M231" s="5" t="inlineStr">
+      <c r="L231" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17923,12 +16782,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L232" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M232" s="5" t="inlineStr">
+      <c r="L232" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -17998,12 +16852,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L233" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M233" s="5" t="inlineStr">
+      <c r="L233" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -18073,12 +16922,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L234" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M234" s="5" t="inlineStr">
+      <c r="L234" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -18148,12 +16992,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L235" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M235" s="5" t="inlineStr">
+      <c r="L235" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -18228,11 +17067,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M236" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N236" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -18303,11 +17137,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M237" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N237" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -18378,11 +17207,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M238" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N238" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -18453,11 +17277,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M239" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N239" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -18483,11 +17302,7 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="D240" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="D240" s="6" t="n"/>
       <c r="E240" s="6" t="inlineStr">
         <is>
           <t>No</t>
@@ -18528,9 +17343,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M240" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N240" s="2" t="inlineStr">
@@ -18603,11 +17418,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M241" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N241" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -18678,11 +17488,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M242" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N242" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -18753,11 +17558,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M243" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N243" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -18828,11 +17628,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M244" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N244" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -18903,11 +17698,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M245" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N245" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -18978,11 +17768,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M246" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N246" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -19053,11 +17838,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M247" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N247" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -19128,11 +17908,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M248" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N248" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19203,11 +17978,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M249" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N249" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19278,11 +18048,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M250" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N250" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19353,11 +18118,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M251" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N251" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19428,11 +18188,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M252" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N252" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19503,11 +18258,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M253" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N253" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19578,11 +18328,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M254" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N254" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19653,11 +18398,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M255" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N255" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19728,11 +18468,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M256" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N256" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19803,11 +18538,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M257" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N257" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19878,11 +18608,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M258" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N258" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -19953,11 +18678,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M259" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N259" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -20028,11 +18748,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M260" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N260" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -20103,11 +18818,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M261" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N261" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -20178,11 +18888,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M262" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N262" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -20253,11 +18958,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M263" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N263" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -20328,11 +19028,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M264" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N264" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -20403,11 +19098,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M265" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N265" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -20478,11 +19168,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M266" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N266" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -20553,11 +19238,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M267" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N267" s="2" t="inlineStr">
         <is>
           <t>USG</t>
@@ -20628,11 +19308,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M268" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N268" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -20703,11 +19378,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M269" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N269" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -20778,11 +19448,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M270" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N270" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -20853,11 +19518,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M271" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N271" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -20918,17 +19578,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K272" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L272" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M272" s="6" t="inlineStr">
+      <c r="K272" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L272" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -20993,17 +19648,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K273" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L273" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M273" s="6" t="inlineStr">
+      <c r="K273" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L273" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -21068,17 +19718,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K274" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L274" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M274" s="6" t="inlineStr">
+      <c r="K274" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L274" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -21143,17 +19788,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K275" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L275" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M275" s="6" t="inlineStr">
+      <c r="K275" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L275" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -21218,17 +19858,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K276" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L276" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M276" s="6" t="inlineStr">
+      <c r="K276" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L276" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -21293,17 +19928,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K277" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L277" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M277" s="6" t="inlineStr">
+      <c r="K277" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L277" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -21368,17 +19998,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K278" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L278" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M278" s="6" t="inlineStr">
+      <c r="K278" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L278" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -21443,17 +20068,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K279" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L279" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M279" s="6" t="inlineStr">
+      <c r="K279" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L279" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -21518,17 +20138,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K280" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L280" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M280" s="6" t="inlineStr">
+      <c r="K280" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L280" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -21593,17 +20208,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K281" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L281" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M281" s="6" t="inlineStr">
+      <c r="K281" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L281" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -21678,11 +20288,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M282" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N282" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -21753,11 +20358,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M283" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N283" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -21828,11 +20428,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M284" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N284" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -21903,11 +20498,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M285" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N285" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -21978,11 +20568,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M286" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N286" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -22053,11 +20638,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M287" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N287" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -22128,11 +20708,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M288" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N288" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -22203,11 +20778,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M289" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N289" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -22278,11 +20848,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M290" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N290" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -22353,11 +20918,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M291" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N291" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -22428,11 +20988,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M292" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N292" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -22503,11 +21058,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M293" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N293" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -22578,11 +21128,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M294" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N294" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -22653,11 +21198,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M295" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N295" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -22728,11 +21268,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M296" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N296" s="2" t="inlineStr">
         <is>
           <t>ECG</t>
@@ -22803,11 +21338,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M297" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N297" s="2" t="inlineStr">
         <is>
           <t>ECG</t>
@@ -22878,11 +21408,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M298" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N298" s="2" t="inlineStr">
         <is>
           <t>ECG</t>
@@ -22953,11 +21478,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M299" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N299" s="2" t="inlineStr">
         <is>
           <t>ECG</t>
@@ -23028,11 +21548,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M300" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N300" s="2" t="inlineStr">
         <is>
           <t>ECG</t>
@@ -23093,17 +21608,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K301" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L301" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M301" s="6" t="inlineStr">
+      <c r="K301" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L301" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -23178,11 +21688,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M302" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -23253,11 +21758,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M303" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N303" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -23328,11 +21828,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M304" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N304" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -23403,11 +21898,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M305" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N305" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -23478,11 +21968,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M306" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N306" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -23553,11 +22038,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M307" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N307" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -23628,11 +22108,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M308" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N308" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -23703,11 +22178,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M309" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N309" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -23778,11 +22248,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M310" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N310" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -23853,11 +22318,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M311" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N311" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -23928,11 +22388,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M312" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N312" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -24003,11 +22458,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M313" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N313" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -24078,11 +22528,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M314" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N314" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -24153,11 +22598,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M315" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N315" s="2" t="inlineStr">
         <is>
           <t>MRI</t>
@@ -24228,11 +22668,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M316" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N316" s="2" t="inlineStr">
         <is>
           <t>ECG</t>
@@ -24303,11 +22738,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M317" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N317" s="2" t="inlineStr">
         <is>
           <t>ECG</t>
@@ -24378,11 +22808,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M318" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N318" s="2" t="inlineStr">
         <is>
           <t>ECG</t>
@@ -24453,11 +22878,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M319" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N319" s="2" t="inlineStr">
         <is>
           <t>ECG</t>
@@ -24524,11 +22944,6 @@
         </is>
       </c>
       <c r="L320" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M320" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
